--- a/Data/register_data.xlsx
+++ b/Data/register_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\datn\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33CB59D4-A1F8-4397-B45E-DED99E98B8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0158BD83-0BB5-4351-85DC-646BECB8D6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E11AF677-B463-4E75-8EB3-301A11E6981C}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E11AF677-B463-4E75-8EB3-301A11E6981C}"/>
   </bookViews>
   <sheets>
     <sheet name="register_data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="36">
   <si>
     <t>lastName</t>
   </si>
@@ -127,13 +127,7 @@
     <t>Mai123</t>
   </si>
   <si>
-    <t>Nguyen</t>
-  </si>
-  <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>mai15@gmail.com</t>
+    <t>Invalid first name</t>
   </si>
 </sst>
 </file>
@@ -994,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E77D5FF8-79E2-4706-8015-254141DE58E0}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="26.5546875" customWidth="1"/>
@@ -1264,6 +1258,9 @@
       <c r="E14">
         <v>123456</v>
       </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1281,16 +1278,8 @@
       <c r="E15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="F15" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Data/register_data.xlsx
+++ b/Data/register_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\datn\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0158BD83-0BB5-4351-85DC-646BECB8D6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25C54B1-4F3C-48B5-BA58-A84E8215E474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E11AF677-B463-4E75-8EB3-301A11E6981C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E11AF677-B463-4E75-8EB3-301A11E6981C}"/>
   </bookViews>
   <sheets>
     <sheet name="register_data" sheetId="1" r:id="rId1"/>
@@ -124,10 +124,10 @@
     <t>thuytien3@gmail.com</t>
   </si>
   <si>
-    <t>Mai123</t>
-  </si>
-  <si>
     <t>Invalid first name</t>
+  </si>
+  <si>
+    <t>"Mai123@"</t>
   </si>
 </sst>
 </file>
@@ -1276,10 +1276,10 @@
         <v>876567435</v>
       </c>
       <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
         <v>34</v>
-      </c>
-      <c r="F15" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Data/register_data.xlsx
+++ b/Data/register_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25C54B1-4F3C-48B5-BA58-A84E8215E474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8065B731-2C89-4490-9ADE-240979ACA38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E11AF677-B463-4E75-8EB3-301A11E6981C}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="35">
   <si>
     <t>lastName</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>thuytien3@gmail.com</t>
-  </si>
-  <si>
-    <t>Invalid first name</t>
   </si>
   <si>
     <t>"Mai123@"</t>
@@ -1276,10 +1273,10 @@
         <v>876567435</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
